--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>PARCIAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,91 +488,91 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:30 - 03:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16:30 - 00:00</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14:00 - 21:30</t>
+          <t>17:00 - 01:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13:30 - 21:00</t>
+          <t>15:00 - 23:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:00 - 03:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>15:00 - 20:30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15:30 - 21:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:30 - 02:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18:00 - 03:00</t>
+          <t>15:00 - 00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15:30 - 23:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00 - 21:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19:30 - 03:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,71 +582,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15:30 - 00:00</t>
+          <t>15:30 - 21:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>15:00 - 21:30</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11:00 - 20:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>15:00 - 21:30</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>18:00 - 03:00</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15:00 - 21:30</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00 - 03:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -656,69 +656,111 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18:00 - 03:00</t>
+          <t>14:00 - 21:30</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18:30 - 03:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18:00 - 03:00</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15:30 - 21:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14:30 - 21:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>16:30 - 01:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>16:30 - 00:00</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>T6</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>18:00 - 03:00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>15:00 - 21:00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>18:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>16:30 - 00:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>15:30 - 00:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>18:00 - 03:00</t>
         </is>
       </c>
     </row>

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -525,32 +525,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:00 - 20:30</t>
+          <t>14:00 - 20:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>18:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>15:00 - 00:00</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>13:30 - 20:30</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>13:30 - 20:30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -582,17 +582,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>12:00 - 21:00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>15:30 - 21:00</t>
+          <t>16:30 - 23:30</t>
         </is>
       </c>
     </row>
@@ -604,19 +604,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>15:00 - 21:30</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>12:00 - 21:00</t>
@@ -629,12 +629,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15:00 - 21:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>15:30 - 20:30</t>
         </is>
       </c>
     </row>
@@ -656,22 +656,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>17:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>18:00 - 02:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>14:00 - 21:30</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -688,17 +688,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:30 - 21:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:30 - 02:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>16:30 - 01:00</t>
+          <t>14:30 - 23:30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16:30 - 00:00</t>
+          <t>16:30 - 23:30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -730,37 +730,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>13:30 - 20:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13:30 - 20:30</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>17:30 - 02:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>18:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>17:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>16:30 - 00:00</t>
         </is>
       </c>
     </row>

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -525,12 +525,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00 - 20:00</t>
+          <t>14:30 - 22:30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>13:30 - 20:30</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>17:00 - 22:30</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>15:00 - 22:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,12 +572,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13:30 - 20:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>20:30 - 02:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>17:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>16:30 - 23:30</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>14:30 - 22:30</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15:30 - 20:30</t>
+          <t>21:00 - 02:00</t>
         </is>
       </c>
     </row>
@@ -646,37 +646,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:30 - 02:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>20:00 - 02:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>18:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>17:30 - 02:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>18:30 - 02:00</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -693,32 +693,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>13:30 - 21:30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>15:00 - 23:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14:30 - 23:30</t>
+          <t>20:30 - 02:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16:30 - 23:30</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30 - 20:30</t>
+          <t>20:00 - 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:30 - 02:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -745,22 +745,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13:30 - 20:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>14:30 - 23:30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>17:00 - 02:00</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>17:30 - 02:00</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>13:00 - 21:30</t>
         </is>
       </c>
     </row>

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,70 +413,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:30 - 02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>20:30 - 02:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,39 +486,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17:00 - 01:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15:00 - 23:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>T1_AbreCierra</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:30 - 22:30</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -540,29 +528,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>19:00 - 02:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17:00 - 22:30</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>T2_AbreCierra</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00 - 22:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -572,12 +560,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 17:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20:30 - 02:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -587,19 +575,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>18:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>17:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>12:00 - 21:00</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>T3_AbreCierra</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -619,148 +607,106 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>12:00 - 18:30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>12:00 - 18:30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14:30 - 22:30</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>21:00 - 02:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>T4_Cierra</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30 - 02:00</t>
+          <t>12:00 - 18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12:00 - 21:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12:00 - 21:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>18:00 - 02:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>17:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>T5</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 20:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13:30 - 21:30</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15:00 - 23:30</t>
+          <t>19:00 - 02:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20:30 - 02:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>T6</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>20:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>18:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>14:30 - 23:30</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>17:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>13:00 - 21:30</t>
+          <t>L</t>
         </is>
       </c>
     </row>

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -466,32 +466,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18:30 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20:30 - 02:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 18:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 19:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>14:00 - 23:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,37 +508,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>17:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>18:00 - 02:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>19:00 - 02:00</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>15:00 - 00:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>16:00 - 01:00</t>
         </is>
       </c>
     </row>
@@ -555,32 +555,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>14:00 - 23:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12:00 - 17:00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>17:00 - 02:00</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>21:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>17:00 - 02:00</t>
         </is>
       </c>
     </row>
@@ -592,37 +592,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12:00 - 18:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>12:00 - 18:30</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>21:00 - 02:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
     </row>
@@ -634,37 +634,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00 - 18:00</t>
+          <t>15:00 - 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>14:00 - 23:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12:00 - 21:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>18:00 - 02:00</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>12:00 - 17:00</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00 - 20:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>20:00 - 02:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,32 +471,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>17:00 - 02:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>12:00 - 18:00</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12:00 - 19:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14:00 - 23:00</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12:00 - 21:00</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
     </row>
@@ -508,12 +508,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>12:00 - 20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>16:00 - 01:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -523,22 +523,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>17:00 - 01:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>19:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15:00 - 00:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>16:00 - 01:00</t>
         </is>
       </c>
     </row>
@@ -550,37 +550,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>13:00 - 22:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14:00 - 23:00</t>
+          <t>13:00 - 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>12:00 - 21:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>21:00 - 02:00</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>16:00 - 01:00</t>
         </is>
       </c>
     </row>
@@ -592,37 +592,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>19:00 - 02:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 21:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>21:00 - 02:00</t>
+          <t>17:00 - 01:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>14:00 - 21:00</t>
         </is>
       </c>
     </row>
@@ -634,37 +634,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00 - 00:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>14:00 - 23:00</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>18:00 - 02:00</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>12:00 - 20:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>12:00 - 18:00</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>12:00 - 21:00</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12:00 - 17:00</t>
         </is>
       </c>
     </row>
@@ -691,20 +691,62 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20:00 - 02:00</t>
+          <t>L</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>15:00 - 23:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>12:00 - 17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>18:00 - 02:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20:00 - 01:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16:00 - 01:00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15:00 - 00:00</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>L</t>
         </is>

--- a/data/outputs/horario_visual.xlsx
+++ b/data/outputs/horario_visual.xlsx
@@ -481,17 +481,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17:00 - 02:00</t>
+          <t>16:00 - 01:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18:00 - 01:00</t>
+          <t>17:00 - 01:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00 - 20:00</t>
+          <t>16:00 - 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17:00 - 01:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>19:00 - 02:00</t>
+          <t>21:00 - 02:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00 - 01:00</t>
+          <t>19:00 - 01:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13:00 - 19:00</t>
+          <t>13:00 - 20:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00 - 02:00</t>
+          <t>12:00 - 20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17:00 - 01:00</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>21:00 - 02:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>12:00 - 21:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>12:00 - 20:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>12:00 - 18:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -718,22 +718,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00 - 01:00</t>
+          <t>18:00 - 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:00 - 02:00</t>
+          <t>19:00 - 02:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20:00 - 01:00</t>
+          <t>18:00 - 01:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>16:00 - 01:00</t>
+          <t>17:00 - 02:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
